--- a/hotshot/downloads/hotshot-math-ifta-worksheet.xlsx
+++ b/hotshot/downloads/hotshot-math-ifta-worksheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jston\AppData\Local\Temp\claude\C--Users-jston-Vault\65110370-aabf-40b0-8298-a551f2aac95d\scratchpad\out\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\Repos\projectcalc-ifta-20261025\hotshot\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEBE76B8-5E4A-41CF-8BE7-8B44F550C41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57594B0-DA79-4D3E-81D9-4D879ECBB758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3072" yWindow="3072" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,21 +110,12 @@
     <t>Truck gross or registered weight (lb)</t>
   </si>
   <si>
-    <t>Gross vehicle weight or registered gross vehicle weight of the truck alone.</t>
-  </si>
-  <si>
     <t>Truck + trailer combination weight (lb)</t>
   </si>
   <si>
-    <t>Gross or registered weight of the whole combination. Leave blank if you run without a trailer.</t>
-  </si>
-  <si>
     <t>Result</t>
   </si>
   <si>
-    <t>Quick check only. 'Meets a QMV test' means IFTA reporting likely applies if you run in two or more member jurisdictions; ask your base jurisdiction to confirm.</t>
-  </si>
-  <si>
     <t>THINGS PEOPLE MISS</t>
   </si>
   <si>
@@ -354,6 +345,15 @@
   </si>
   <si>
     <t>Made by Hotshot Math. Provided as is, free to use and to share unchanged. Nothing here is affiliated with or endorsed by IFTA, Inc. or any government agency.</t>
+  </si>
+  <si>
+    <t>Gross vehicle weight or registered gross vehicle weight of the truck alone - use whichever is higher.</t>
+  </si>
+  <si>
+    <t>Gross or registered weight of the whole combination - use whichever is higher. Leave blank if you run without a trailer.</t>
+  </si>
+  <si>
+    <t>Quick check only. 'Meets a QMV test' means IFTA reporting likely applies if you run in two or more member jurisdictions. 'Does not meet' is not a ruling. Either way, ask your base jurisdiction to confirm.</t>
   </si>
 </sst>
 </file>
@@ -593,11 +593,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,38 +1069,38 @@
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="2" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="2" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B26" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="50" t="str">
-        <f>IF(AND(N(C23)=0,N(C24)=0,N(C25)=0),"Enter your numbers",IF(OR(AND(N(C23)=2,N(C24)&gt;26000),N(C23)&gt;=3,N(C25)&gt;26000),"Meets a QMV test","Does not meet a QMV test"))</f>
+        <v>24</v>
+      </c>
+      <c r="C26" s="51" t="str">
+        <f>IF(AND(N(C23)=0,N(C24)=0,N(C25)=0),"Enter your numbers",IF(OR(AND(N(C23)=2,N(C24)&gt;26000),N(C23)&gt;=3,N(C25)&gt;26000),"Meets a QMV test","Does not meet a QMV test on these numbers - confirm with your base jurisdiction before you skip IFTA"))</f>
         <v>Enter your numbers</v>
       </c>
-      <c r="D26" s="51"/>
+      <c r="D26" s="52"/>
     </row>
     <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="52" t="s">
-        <v>27</v>
+      <c r="B27" s="50" t="s">
+        <v>104</v>
       </c>
       <c r="C27" s="49"/>
       <c r="D27" s="49"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1108,67 +1108,67 @@
     </row>
     <row r="30" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
     </row>
     <row r="31" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C31" s="49"/>
       <c r="D31" s="49"/>
     </row>
     <row r="32" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="48" t="s">
         <v>29</v>
-      </c>
-      <c r="B32" s="48" t="s">
-        <v>32</v>
       </c>
       <c r="C32" s="49"/>
       <c r="D32" s="49"/>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C33" s="49"/>
       <c r="D33" s="49"/>
     </row>
     <row r="34" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B34" s="48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C34" s="49"/>
       <c r="D34" s="49"/>
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1176,59 +1176,52 @@
     </row>
     <row r="38" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="48" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C38" s="49"/>
       <c r="D38" s="15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="48" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C39" s="49"/>
       <c r="D39" s="15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="48" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C40" s="49"/>
       <c r="D40" s="15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C41" s="49"/>
       <c r="D41" s="15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B44" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
@@ -1240,11 +1233,18 @@
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B39:C39"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" allowBlank="1" errorTitle="Axles" error="Enter a whole number of axles (1 to 12)." sqref="C23" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1286,56 +1286,56 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B5" s="20">
         <v>2026</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B6" s="21">
         <f>IFERROR(INDEX('Due dates'!$E$6:$E$9,MATCH($B$4,'Due dates'!$A$6:$A$9,0)),"")</f>
         <v>46328</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B7" s="22">
         <f>IF(N($C$45)&gt;0,$B$45/$C$45,"")</f>
@@ -1344,16 +1344,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B9" s="22">
         <f>IF(N($B$8)&gt;0,$B$8,IF(ISNUMBER($B$7),$B$7,""))</f>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B10" s="25" t="str">
         <f>IF(COUNT($F$15:$F$44)=0,"enter rates",$G$45)</f>
@@ -1371,52 +1371,52 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B11" s="26">
         <f>SUMPRODUCT((((($B$15:$B$44&lt;&gt;"")+($C$15:$C$44&lt;&gt;""))&gt;0)*($F$15:$F$44="")))</f>
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="E14" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="F14" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="G14" s="28" t="s">
         <v>69</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="29" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B15" s="13">
         <v>3100</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="29" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B16" s="13">
         <v>1800</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="29" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B17" s="13">
         <v>1000</v>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B45" s="35">
         <f>SUM(B15:B44)</f>
@@ -2000,22 +2000,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2072,12 +2072,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" s="49"/>
       <c r="C2" s="49"/>
@@ -2087,47 +2087,47 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B3" s="26">
         <f>'Quarter worksheet'!$B$5</f>
         <v>2026</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="E5" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>88</v>
-      </c>
       <c r="F5" s="28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C6" s="43">
         <f>DATE($B$3+0,4,30)</f>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="41" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C7" s="43">
         <f>DATE($B$3+0,7,31)</f>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C8" s="43">
         <f>DATE($B$3+0,10,31)</f>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="41" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C9" s="43">
         <f>DATE($B$3+1,1,31)</f>
@@ -2220,35 +2220,35 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="40" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="E13" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>88</v>
-      </c>
       <c r="F13" s="28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C14" s="43">
         <f>DATE(($B$3+1)+0,4,30)</f>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="41" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C15" s="43">
         <f>DATE(($B$3+1)+0,7,31)</f>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C16" s="43">
         <f>DATE(($B$3+1)+0,10,31)</f>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="41" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B17" s="42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C17" s="43">
         <f>DATE(($B$3+1)+1,1,31)</f>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="19" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B19" s="49"/>
       <c r="C19" s="49"/>
@@ -2351,22 +2351,22 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="47" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2396,42 +2396,42 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
